--- a/data/sample/applications_sample.xlsx
+++ b/data/sample/applications_sample.xlsx
@@ -495,7 +495,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>North Analytics</t>
+          <t>Vertex Energy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -510,7 +510,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -519,14 +519,12 @@
         </is>
       </c>
       <c r="G2" s="1" t="n">
-        <v>46197</v>
+        <v>46192</v>
       </c>
       <c r="H2" t="inlineStr"/>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" s="1" t="n">
-        <v>46213</v>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -538,31 +536,31 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Bright Bank</t>
+          <t>Blue Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G3" s="1" t="n">
-        <v>46204</v>
+        <v>46203</v>
       </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
@@ -579,12 +577,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Vertex Media</t>
+          <t>Summit Labs</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -599,18 +597,14 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G4" s="1" t="n">
-        <v>46204</v>
-      </c>
-      <c r="H4" s="1" t="n">
-        <v>46217</v>
-      </c>
-      <c r="I4" s="1" t="n">
-        <v>46229</v>
-      </c>
+        <v>46206</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
@@ -624,12 +618,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Vertex Labs</t>
+          <t>North Retail</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -644,18 +638,16 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G5" s="1" t="n">
-        <v>46209</v>
+        <v>46212</v>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" s="1" t="n">
-        <v>46249</v>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
     </row>
@@ -667,39 +659,39 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Cedar Labs</t>
+          <t>Vertex Health</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="G6" s="1" t="n">
-        <v>46210</v>
+        <v>46213</v>
       </c>
       <c r="H6" s="1" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" s="1" t="n">
-        <v>46224</v>
+        <v>46230</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
@@ -717,17 +709,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -736,17 +728,11 @@
         </is>
       </c>
       <c r="G7" s="1" t="n">
-        <v>46210</v>
-      </c>
-      <c r="H7" s="1" t="n">
-        <v>46224</v>
-      </c>
-      <c r="I7" s="1" t="n">
-        <v>46236</v>
-      </c>
-      <c r="J7" s="1" t="n">
-        <v>46243</v>
-      </c>
+        <v>46219</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
@@ -759,36 +745,38 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quantum Insurance</t>
+          <t>Quantum Logistics</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G8" s="1" t="n">
-        <v>46216</v>
+        <v>46219</v>
       </c>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" s="1" t="n">
+        <v>46256</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
     </row>
@@ -800,41 +788,35 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Harbor Analytics</t>
+          <t>Nova Bank</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G9" s="1" t="n">
-        <v>46216</v>
-      </c>
-      <c r="H9" s="1" t="n">
-        <v>46221</v>
-      </c>
-      <c r="I9" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="J9" s="1" t="n">
-        <v>46242</v>
-      </c>
+        <v>46220</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
@@ -847,22 +829,22 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Summit Logistics</t>
+          <t>Blue Retail</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -871,14 +853,12 @@
         </is>
       </c>
       <c r="G10" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="H10" t="inlineStr"/>
       <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" s="1" t="n">
-        <v>46240</v>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
     </row>
@@ -890,22 +870,22 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Summit Energy</t>
+          <t>Nova Media</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -914,17 +894,11 @@
         </is>
       </c>
       <c r="G11" s="1" t="n">
-        <v>46219</v>
-      </c>
-      <c r="H11" s="1" t="n">
-        <v>46226</v>
-      </c>
-      <c r="I11" s="1" t="n">
-        <v>46233</v>
-      </c>
-      <c r="J11" s="1" t="n">
-        <v>46252</v>
-      </c>
+        <v>46223</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
@@ -937,7 +911,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Vertex Logistics</t>
+          <t>Blue Media</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -952,22 +926,26 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G12" s="1" t="n">
-        <v>46220</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
+        <v>46223</v>
+      </c>
+      <c r="H12" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="I12" s="1" t="n">
+        <v>46236</v>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" s="1" t="n">
-        <v>46238</v>
+        <v>46247</v>
       </c>
       <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr"/>
@@ -980,38 +958,36 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Lumen Media</t>
+          <t>North Media</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="G13" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
-      <c r="K13" s="1" t="n">
-        <v>46239</v>
-      </c>
+      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
     </row>
@@ -1023,22 +999,22 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Bright Health</t>
+          <t>Bright Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1064,7 +1040,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Cedar Insurance</t>
+          <t>Atlas Labs</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1084,18 +1060,16 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G15" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" s="1" t="n">
-        <v>46235</v>
-      </c>
+      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr"/>
     </row>
@@ -1107,7 +1081,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Summit Media</t>
+          <t>Blue Analytics</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1117,7 +1091,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1127,13 +1101,15 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G16" s="1" t="n">
-        <v>46223</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>46226</v>
+      </c>
+      <c r="H16" s="1" t="n">
+        <v>46236</v>
+      </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
@@ -1148,7 +1124,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Atlas Energy</t>
+          <t>Blue Media</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1158,31 +1134,25 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G17" s="1" t="n">
-        <v>46224</v>
-      </c>
-      <c r="H17" s="1" t="n">
-        <v>46238</v>
-      </c>
-      <c r="I17" s="1" t="n">
-        <v>46242</v>
-      </c>
-      <c r="J17" s="1" t="n">
-        <v>46262</v>
-      </c>
+        <v>46226</v>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
@@ -1195,17 +1165,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Nova Mobility</t>
+          <t>North Health</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1215,19 +1185,21 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Referral</t>
         </is>
       </c>
       <c r="G18" s="1" t="n">
-        <v>46225</v>
+        <v>46230</v>
       </c>
       <c r="H18" s="1" t="n">
-        <v>46228</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
+        <v>46236</v>
+      </c>
+      <c r="I18" s="1" t="n">
+        <v>46242</v>
+      </c>
       <c r="J18" t="inlineStr"/>
       <c r="K18" s="1" t="n">
-        <v>46230</v>
+        <v>46256</v>
       </c>
       <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr"/>
@@ -1240,7 +1212,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Bright Energy</t>
+          <t>Nova Labs</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1255,7 +1227,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1264,12 +1236,14 @@
         </is>
       </c>
       <c r="G19" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" s="1" t="n">
+        <v>46270</v>
+      </c>
       <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr"/>
     </row>
@@ -1281,31 +1255,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Blue Media</t>
+          <t>Silver Retail</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G20" s="1" t="n">
-        <v>46227</v>
+        <v>46232</v>
       </c>
       <c r="H20" t="inlineStr"/>
       <c r="I20" t="inlineStr"/>
@@ -1322,7 +1296,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Atlas Logistics</t>
+          <t>North Insurance</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1332,21 +1306,21 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G21" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
@@ -1363,22 +1337,22 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cedar Health</t>
+          <t>Atlas Retail</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1387,12 +1361,14 @@
         </is>
       </c>
       <c r="G22" s="1" t="n">
-        <v>46230</v>
+        <v>46234</v>
       </c>
       <c r="H22" t="inlineStr"/>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" s="1" t="n">
+        <v>46272</v>
+      </c>
       <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr"/>
     </row>
@@ -1404,12 +1380,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vertex Energy</t>
+          <t>Blue Mobility</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1424,16 +1400,22 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G23" s="1" t="n">
-        <v>46230</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
+        <v>46237</v>
+      </c>
+      <c r="H23" s="1" t="n">
+        <v>46249</v>
+      </c>
+      <c r="I23" s="1" t="n">
+        <v>46254</v>
+      </c>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" s="1" t="n">
+        <v>46267</v>
+      </c>
       <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr"/>
     </row>
@@ -1445,22 +1427,22 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cedar Retail</t>
+          <t>Blue Insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1469,7 +1451,7 @@
         </is>
       </c>
       <c r="G24" s="1" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr"/>
@@ -1486,31 +1468,31 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>North Logistics</t>
+          <t>Cedar Energy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G25" s="1" t="n">
-        <v>46230</v>
+        <v>46237</v>
       </c>
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
@@ -1527,17 +1509,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Lumen Mobility</t>
+          <t>Silver Labs</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1547,21 +1529,15 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="G26" s="1" t="n">
-        <v>46231</v>
-      </c>
-      <c r="H26" s="1" t="n">
-        <v>46244</v>
-      </c>
-      <c r="I26" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="J26" s="1" t="n">
-        <v>46265</v>
-      </c>
+        <v>46237</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
@@ -1574,31 +1550,31 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Harbor Labs</t>
+          <t>North Bank</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G27" s="1" t="n">
-        <v>46232</v>
+        <v>46237</v>
       </c>
       <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr"/>
@@ -1615,17 +1591,17 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Atlas Retail</t>
+          <t>Silver Health</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1635,16 +1611,18 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G28" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" s="1" t="n">
+        <v>46247</v>
+      </c>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
     </row>
@@ -1656,7 +1634,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>North Logistics</t>
+          <t>Blue Analytics</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1666,21 +1644,21 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G29" s="1" t="n">
-        <v>46233</v>
+        <v>46238</v>
       </c>
       <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr"/>
@@ -1697,7 +1675,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bright Retail</t>
+          <t>Nova Bank</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1721,7 +1699,7 @@
         </is>
       </c>
       <c r="G30" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="H30" t="inlineStr"/>
       <c r="I30" t="inlineStr"/>
@@ -1738,7 +1716,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Bright Analytics</t>
+          <t>Nova Bank</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1753,24 +1731,22 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G31" s="1" t="n">
-        <v>46237</v>
-      </c>
-      <c r="H31" s="1" t="n">
-        <v>46241</v>
-      </c>
+        <v>46238</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr"/>
       <c r="K31" s="1" t="n">
-        <v>46246</v>
+        <v>46276</v>
       </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
@@ -1783,22 +1759,22 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Harbor Mobility</t>
+          <t>Bright Retail</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1807,7 +1783,7 @@
         </is>
       </c>
       <c r="G32" s="1" t="n">
-        <v>46237</v>
+        <v>46241</v>
       </c>
       <c r="H32" t="inlineStr"/>
       <c r="I32" t="inlineStr"/>
@@ -1824,22 +1800,22 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Summit Health</t>
+          <t>Nova Health</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1848,14 +1824,12 @@
         </is>
       </c>
       <c r="G33" s="1" t="n">
-        <v>46237</v>
+        <v>46244</v>
       </c>
       <c r="H33" t="inlineStr"/>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr"/>
-      <c r="K33" s="1" t="n">
-        <v>46244</v>
-      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr"/>
     </row>
@@ -1867,7 +1841,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Nova Logistics</t>
+          <t>Cedar Analytics</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1887,11 +1861,11 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G34" s="1" t="n">
-        <v>46238</v>
+        <v>46244</v>
       </c>
       <c r="H34" t="inlineStr"/>
       <c r="I34" t="inlineStr"/>
@@ -1908,17 +1882,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">  Blue Energy</t>
+          <t xml:space="preserve">  Cedar Analytics</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1928,22 +1902,16 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G35" s="1" t="n">
-        <v>46239</v>
-      </c>
-      <c r="H35" s="1" t="n">
-        <v>46241</v>
-      </c>
-      <c r="I35" s="1" t="n">
-        <v>46250</v>
-      </c>
+        <v>46245</v>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" s="1" t="n">
-        <v>46260</v>
-      </c>
+      <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
       <c r="M35" t="inlineStr"/>
     </row>
@@ -1955,12 +1923,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cedar Analytics</t>
+          <t>Blue Logistics</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1975,16 +1943,18 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G36" s="1" t="n">
-        <v>46239</v>
+        <v>46246</v>
       </c>
       <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" s="1" t="n">
+        <v>46251</v>
+      </c>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
     </row>
@@ -1996,7 +1966,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Atlas Bank</t>
+          <t>Summit Mobility</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2006,26 +1976,32 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G37" s="1" t="n">
-        <v>46240</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
+        <v>46246</v>
+      </c>
+      <c r="H37" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="I37" s="1" t="n">
+        <v>46255</v>
+      </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" s="1" t="n">
+        <v>46260</v>
+      </c>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
     </row>
@@ -2037,12 +2013,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Silver Insurance</t>
+          <t>Blue Insurance</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2061,7 +2037,7 @@
         </is>
       </c>
       <c r="G38" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="H38" t="inlineStr"/>
       <c r="I38" t="inlineStr"/>
@@ -2078,17 +2054,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cedar Labs</t>
+          <t>Vertex Health</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2098,11 +2074,11 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G39" s="1" t="n">
-        <v>46244</v>
+        <v>46247</v>
       </c>
       <c r="H39" t="inlineStr"/>
       <c r="I39" t="inlineStr"/>
@@ -2119,12 +2095,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Summit Mobility</t>
+          <t>Lumen Retail</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2139,11 +2115,11 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G40" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
@@ -2160,22 +2136,22 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Quantum Labs</t>
+          <t>North Retail</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2184,14 +2160,18 @@
         </is>
       </c>
       <c r="G41" s="1" t="n">
-        <v>46246</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" s="1" t="n">
-        <v>46272</v>
-      </c>
+        <v>46247</v>
+      </c>
+      <c r="H41" s="1" t="n">
+        <v>46256</v>
+      </c>
+      <c r="I41" s="1" t="n">
+        <v>46263</v>
+      </c>
+      <c r="J41" s="1" t="n">
+        <v>46273</v>
+      </c>
+      <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
     </row>
@@ -2203,7 +2183,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Vertex Health</t>
+          <t>Blue Health</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2213,7 +2193,7 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
@@ -2223,17 +2203,19 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G42" s="1" t="n">
-        <v>46247</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>46251</v>
+      </c>
+      <c r="H42" s="1" t="n">
+        <v>46262</v>
+      </c>
       <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr"/>
       <c r="K42" s="1" t="n">
-        <v>46284</v>
+        <v>46268</v>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
@@ -2246,31 +2228,31 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Lumen Insurance</t>
+          <t>Lumen Labs</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G43" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr"/>
@@ -2287,31 +2269,31 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Harbor Mobility</t>
+          <t>Nova Media</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G44" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="H44" t="inlineStr"/>
       <c r="I44" t="inlineStr"/>
@@ -2328,12 +2310,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cedar Insurance</t>
+          <t>Bright Health</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2348,11 +2330,11 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G45" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr"/>
@@ -2369,12 +2351,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Bright Mobility</t>
+          <t>Lumen Media</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2389,17 +2371,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G46" s="1" t="n">
-        <v>46248</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
+        <v>46252</v>
+      </c>
+      <c r="H46" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="I46" s="1" t="n">
+        <v>46270</v>
+      </c>
       <c r="J46" t="inlineStr"/>
       <c r="K46" s="1" t="n">
-        <v>46283</v>
+        <v>46278</v>
       </c>
       <c r="L46" t="inlineStr"/>
       <c r="M46" t="inlineStr"/>
@@ -2412,17 +2398,17 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Harbor Insurance</t>
+          <t>Harbor Media</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2432,16 +2418,22 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Referral</t>
         </is>
       </c>
       <c r="G47" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
+        <v>46254</v>
+      </c>
+      <c r="H47" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="I47" s="1" t="n">
+        <v>46280</v>
+      </c>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" s="1" t="n">
+        <v>46288</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
     </row>
@@ -2458,31 +2450,35 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G48" s="1" t="n">
-        <v>46251</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>46254</v>
+      </c>
+      <c r="H48" s="1" t="n">
+        <v>46268</v>
+      </c>
       <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" s="1" t="n">
+        <v>46277</v>
+      </c>
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr"/>
     </row>
@@ -2494,12 +2490,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>North Retail</t>
+          <t>Harbor Logistics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2514,11 +2510,11 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G49" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="H49" t="inlineStr"/>
       <c r="I49" t="inlineStr"/>
@@ -2535,22 +2531,22 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cedar Insurance</t>
+          <t>North Health</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2559,10 +2555,10 @@
         </is>
       </c>
       <c r="G50" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="H50" s="1" t="n">
         <v>46252</v>
-      </c>
-      <c r="H50" s="1" t="n">
-        <v>46249</v>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr"/>
@@ -2578,36 +2574,42 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Quantum Health</t>
+          <t>Quantum Retail</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G51" s="1" t="n">
-        <v>46253</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
+        <v>46255</v>
+      </c>
+      <c r="H51" s="1" t="n">
+        <v>46269</v>
+      </c>
+      <c r="I51" s="1" t="n">
+        <v>46279</v>
+      </c>
       <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" s="1" t="n">
+        <v>46288</v>
+      </c>
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr"/>
     </row>
@@ -2619,7 +2621,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Harbor Energy</t>
+          <t>Atlas Energy</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2629,7 +2631,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2639,16 +2641,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G52" s="1" t="n">
-        <v>46254</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>46258</v>
+      </c>
+      <c r="H52" s="1" t="n">
+        <v>46261</v>
+      </c>
       <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
+      <c r="K52" s="1" t="n">
+        <v>46271</v>
+      </c>
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr"/>
     </row>
@@ -2660,12 +2666,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Lumen Labs</t>
+          <t>Summit Analytics</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2680,16 +2686,18 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G53" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="H53" t="inlineStr"/>
       <c r="I53" t="inlineStr"/>
       <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
+      <c r="K53" s="1" t="n">
+        <v>46273</v>
+      </c>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
     </row>
@@ -2701,17 +2709,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Nova Mobility</t>
+          <t>Bright Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2721,18 +2729,16 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="H54" t="inlineStr"/>
       <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr"/>
-      <c r="K54" s="1" t="n">
-        <v>46269</v>
-      </c>
+      <c r="K54" t="inlineStr"/>
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr"/>
     </row>
@@ -2744,17 +2750,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blue Mobility</t>
+          <t>Cedar Retail</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2764,17 +2770,17 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr"/>
       <c r="J55" t="inlineStr"/>
       <c r="K55" s="1" t="n">
-        <v>46284</v>
+        <v>46290</v>
       </c>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr"/>
@@ -2787,12 +2793,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Blue Bank</t>
+          <t>Nova Health</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2802,18 +2808,20 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G56" s="1" t="n">
         <v>46258</v>
       </c>
-      <c r="H56" t="inlineStr"/>
+      <c r="H56" s="1" t="n">
+        <v>46261</v>
+      </c>
       <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
@@ -2828,7 +2836,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Quantum Insurance</t>
+          <t>Harbor Retail</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2838,17 +2846,17 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G57" s="1" t="n">
@@ -2857,9 +2865,7 @@
       <c r="H57" t="inlineStr"/>
       <c r="I57" t="inlineStr"/>
       <c r="J57" t="inlineStr"/>
-      <c r="K57" s="1" t="n">
-        <v>46279</v>
-      </c>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="M57" t="inlineStr"/>
     </row>
@@ -2871,12 +2877,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Lumen Insurance</t>
+          <t>Harbor Analytics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2895,14 +2901,12 @@
         </is>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr"/>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" s="1" t="n">
-        <v>46280</v>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
     </row>
@@ -2914,17 +2918,17 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Harbor Logistics</t>
+          <t>Quantum Health</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2934,7 +2938,7 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G59" s="1" t="n">
@@ -2943,7 +2947,9 @@
       <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
+      <c r="K59" s="1" t="n">
+        <v>46265</v>
+      </c>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr"/>
     </row>
@@ -2955,17 +2961,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>North Retail</t>
+          <t>North Health</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2975,18 +2981,16 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46260</v>
+        <v>46259</v>
       </c>
       <c r="H60" t="inlineStr"/>
       <c r="I60" t="inlineStr"/>
       <c r="J60" t="inlineStr"/>
-      <c r="K60" s="1" t="n">
-        <v>46268</v>
-      </c>
+      <c r="K60" t="inlineStr"/>
       <c r="L60" t="inlineStr"/>
       <c r="M60" t="inlineStr"/>
     </row>
@@ -2998,7 +3002,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Bright Analytics</t>
+          <t>Blue Energy</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -3008,17 +3012,17 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G61" s="1" t="n">
@@ -3039,17 +3043,17 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Cedar Insurance</t>
+          <t>Nova Retail</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -3063,12 +3067,14 @@
         </is>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="H62" t="inlineStr"/>
       <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
+      <c r="K62" s="1" t="n">
+        <v>46279</v>
+      </c>
       <c r="L62" t="inlineStr"/>
       <c r="M62" t="inlineStr"/>
     </row>
@@ -3080,17 +3086,17 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Lumen Health</t>
+          <t>Atlas Health</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -3100,21 +3106,15 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46260</v>
-      </c>
-      <c r="H63" s="1" t="n">
         <v>46265</v>
       </c>
-      <c r="I63" s="1" t="n">
-        <v>46271</v>
-      </c>
-      <c r="J63" s="1" t="n">
-        <v>46286</v>
-      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="L63" t="inlineStr"/>
       <c r="M63" t="inlineStr"/>
@@ -3127,17 +3127,17 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Vertex Mobility</t>
+          <t>Atlas Bank</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3147,16 +3147,18 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46260</v>
+        <v>46265</v>
       </c>
       <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr"/>
       <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
+      <c r="K64" s="1" t="n">
+        <v>46286</v>
+      </c>
       <c r="L64" t="inlineStr"/>
       <c r="M64" t="inlineStr"/>
     </row>
@@ -3168,38 +3170,36 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vertex Health</t>
+          <t>Cedar Analytics</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr"/>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" s="1" t="n">
-        <v>46268</v>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
     </row>
@@ -3211,38 +3211,36 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Bright Mobility</t>
+          <t>North Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="H66" t="inlineStr"/>
       <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
-      <c r="K66" s="1" t="n">
-        <v>46296</v>
-      </c>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="M66" t="inlineStr"/>
     </row>
@@ -3254,7 +3252,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Silver Health</t>
+          <t>Bright Labs</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -3264,26 +3262,28 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="H67" t="inlineStr"/>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
+      <c r="K67" s="1" t="n">
+        <v>46276</v>
+      </c>
       <c r="L67" t="inlineStr"/>
       <c r="M67" t="inlineStr"/>
     </row>
@@ -3295,36 +3295,38 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>North Insurance</t>
+          <t>Blue Logistics</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="H68" t="inlineStr"/>
       <c r="I68" t="inlineStr"/>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
+      <c r="K68" s="1" t="n">
+        <v>46293</v>
+      </c>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
     </row>
@@ -3336,17 +3338,17 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Harbor Analytics</t>
+          <t>North Insurance</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -3356,17 +3358,21 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46262</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
-      <c r="I69" t="inlineStr"/>
+        <v>46265</v>
+      </c>
+      <c r="H69" s="1" t="n">
+        <v>46270</v>
+      </c>
+      <c r="I69" s="1" t="n">
+        <v>46277</v>
+      </c>
       <c r="J69" t="inlineStr"/>
       <c r="K69" s="1" t="n">
-        <v>46279</v>
+        <v>46282</v>
       </c>
       <c r="L69" t="inlineStr"/>
       <c r="M69" t="inlineStr"/>
@@ -3379,31 +3385,31 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Silver Energy</t>
+          <t>Lumen Insurance</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr"/>
@@ -3420,12 +3426,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cedar Media</t>
+          <t>Silver Analytics</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -3435,16 +3441,16 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr"/>
@@ -3461,38 +3467,36 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Bright Mobility</t>
+          <t>Summit Bank</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="H72" t="inlineStr"/>
       <c r="I72" t="inlineStr"/>
       <c r="J72" t="inlineStr"/>
-      <c r="K72" s="1" t="n">
-        <v>46275</v>
-      </c>
+      <c r="K72" t="inlineStr"/>
       <c r="L72" t="inlineStr"/>
       <c r="M72" t="inlineStr"/>
     </row>
@@ -3504,38 +3508,36 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Nova Media</t>
+          <t>Cedar Bank</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr"/>
       <c r="J73" t="inlineStr"/>
-      <c r="K73" s="1" t="n">
-        <v>46279</v>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
     </row>
@@ -3547,36 +3549,38 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Silver Analytics</t>
+          <t>Summit Energy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
+      <c r="K74" s="1" t="n">
+        <v>46293</v>
+      </c>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
     </row>
@@ -3588,33 +3592,35 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>North Logistics</t>
+          <t>Atlas Health</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Referral</t>
         </is>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46265</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>46268</v>
+      </c>
+      <c r="H75" s="1" t="n">
+        <v>46277</v>
+      </c>
       <c r="I75" t="inlineStr"/>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
@@ -3629,38 +3635,36 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Lumen Analytics</t>
+          <t>North Energy</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46265</v>
+        <v>46268</v>
       </c>
       <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
-      <c r="K76" s="1" t="n">
-        <v>46274</v>
-      </c>
+      <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
       <c r="M76" t="inlineStr"/>
     </row>
@@ -3672,12 +3676,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Atlas Retail</t>
+          <t>Bright Analytics</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -3692,7 +3696,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G77" s="1" t="n">
@@ -3713,27 +3717,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Lumen Labs</t>
+          <t>Nova Bank</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G78" s="1" t="n">
@@ -3742,7 +3746,9 @@
       <c r="H78" t="inlineStr"/>
       <c r="I78" t="inlineStr"/>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr"/>
+      <c r="K78" s="1" t="n">
+        <v>46295</v>
+      </c>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
     </row>
@@ -3754,7 +3760,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Quantum Insurance</t>
+          <t>Lumen Retail</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -3764,17 +3770,17 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G79" s="1" t="n">
@@ -3783,9 +3789,7 @@
       <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr"/>
       <c r="J79" t="inlineStr"/>
-      <c r="K79" s="1" t="n">
-        <v>46286</v>
-      </c>
+      <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
     </row>
@@ -3797,7 +3801,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Harbor Insurance</t>
+          <t>Nova Insurance</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -3807,30 +3811,26 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="H80" s="1" t="n">
         <v>46272</v>
       </c>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" s="1" t="n">
-        <v>46282</v>
-      </c>
+      <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
       <c r="M80" t="inlineStr"/>
     </row>
@@ -3842,22 +3842,22 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>North Media</t>
+          <t>Bright Labs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3866,12 +3866,16 @@
         </is>
       </c>
       <c r="G81" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
+        <v>46272</v>
+      </c>
+      <c r="H81" s="1" t="n">
+        <v>46285</v>
+      </c>
       <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" s="1" t="n">
+        <v>46288</v>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
     </row>
@@ -3883,17 +3887,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Summit Insurance</t>
+          <t>Bright Logistics</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3903,7 +3907,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G82" s="1" t="n">
@@ -3912,7 +3916,9 @@
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr"/>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr"/>
+      <c r="K82" s="1" t="n">
+        <v>46281</v>
+      </c>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
     </row>
@@ -3929,22 +3935,22 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G83" s="1" t="n">
@@ -3953,9 +3959,7 @@
       <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr"/>
       <c r="J83" t="inlineStr"/>
-      <c r="K83" s="1" t="n">
-        <v>46290</v>
-      </c>
+      <c r="K83" t="inlineStr"/>
       <c r="L83" t="inlineStr"/>
       <c r="M83" t="inlineStr"/>
     </row>
@@ -3967,7 +3971,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Atlas Analytics</t>
+          <t>Atlas Retail</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -3982,12 +3986,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G84" s="1" t="n">
@@ -4008,27 +4012,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Vertex Bank</t>
+          <t>North Analytics</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G85" s="1" t="n">
@@ -4037,7 +4041,9 @@
       <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr"/>
       <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
+      <c r="K85" s="1" t="n">
+        <v>46282</v>
+      </c>
       <c r="L85" t="inlineStr"/>
       <c r="M85" t="inlineStr"/>
     </row>
@@ -4049,27 +4055,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Blue Labs</t>
+          <t>Nova Logistics</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G86" s="1" t="n">
@@ -4090,38 +4096,34 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Silver Media</t>
+          <t>Nova Labs</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G87" s="1" t="n">
         <v>46272</v>
       </c>
-      <c r="H87" s="1" t="n">
-        <v>46281</v>
-      </c>
-      <c r="I87" s="1" t="n">
-        <v>46293</v>
-      </c>
+      <c r="H87" t="inlineStr"/>
+      <c r="I87" t="inlineStr"/>
       <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="L87" t="inlineStr"/>
@@ -4135,17 +4137,17 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Nova Analytics</t>
+          <t>Nova Mobility</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
@@ -4155,11 +4157,11 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G88" s="1" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr"/>
@@ -4176,38 +4178,40 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Lumen Energy</t>
+          <t>Summit Energy</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G89" s="1" t="n">
-        <v>46274</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
-      <c r="I89" t="inlineStr"/>
+        <v>46273</v>
+      </c>
+      <c r="H89" s="1" t="n">
+        <v>46284</v>
+      </c>
+      <c r="I89" s="1" t="n">
+        <v>46295</v>
+      </c>
       <c r="J89" t="inlineStr"/>
-      <c r="K89" s="1" t="n">
-        <v>46294</v>
-      </c>
+      <c r="K89" t="inlineStr"/>
       <c r="L89" t="inlineStr"/>
       <c r="M89" t="inlineStr"/>
     </row>
@@ -4219,17 +4223,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Bright Labs</t>
+          <t>Bright Retail</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -4239,7 +4243,7 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G90" s="1" t="n">
@@ -4260,27 +4264,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Cedar Analytics</t>
+          <t>Nova Energy</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G91" s="1" t="n">
@@ -4301,12 +4305,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Quantum Health</t>
+          <t>Blue Analytics</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -4316,7 +4320,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -4342,12 +4346,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Summit Media</t>
+          <t>North Media</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -4362,15 +4366,13 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G93" s="1" t="n">
-        <v>46275</v>
-      </c>
-      <c r="H93" s="1" t="n">
-        <v>46289</v>
-      </c>
+        <v>46276</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
       <c r="I93" t="inlineStr"/>
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr"/>
@@ -4385,40 +4387,36 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Harbor Labs</t>
+          <t>Silver Logistics</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Referral</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G94" s="1" t="n">
         <v>46276</v>
       </c>
-      <c r="H94" s="1" t="n">
-        <v>46283</v>
-      </c>
+      <c r="H94" t="inlineStr"/>
       <c r="I94" t="inlineStr"/>
       <c r="J94" t="inlineStr"/>
-      <c r="K94" s="1" t="n">
-        <v>46288</v>
-      </c>
+      <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr"/>
     </row>
@@ -4430,12 +4428,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Bright Bank</t>
+          <t>Harbor Retail</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -4454,7 +4452,7 @@
         </is>
       </c>
       <c r="G95" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="H95" t="inlineStr"/>
       <c r="I95" t="inlineStr"/>
@@ -4471,12 +4469,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Atlas Media</t>
+          <t>Quantum Retail</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -4491,16 +4489,18 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G96" s="1" t="n">
-        <v>46276</v>
+        <v>46279</v>
       </c>
       <c r="H96" t="inlineStr"/>
       <c r="I96" t="inlineStr"/>
       <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
+      <c r="K96" s="1" t="n">
+        <v>46293</v>
+      </c>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
     </row>
@@ -4512,27 +4512,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Cedar Logistics</t>
+          <t>Blue Media</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G97" s="1" t="n">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Quantum Media</t>
+          <t>Silver Mobility</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -4563,7 +4563,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4573,13 +4573,15 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="G98" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="H98" t="inlineStr"/>
+      <c r="H98" s="1" t="n">
+        <v>46281</v>
+      </c>
       <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
@@ -4594,12 +4596,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Vertex Bank</t>
+          <t>Vertex Retail</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -4609,20 +4611,18 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G99" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="H99" s="1" t="n">
-        <v>46293</v>
-      </c>
+      <c r="H99" t="inlineStr"/>
       <c r="I99" t="inlineStr"/>
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr"/>
@@ -4637,12 +4637,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Summit Energy</t>
+          <t>Silver Mobility</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -4652,7 +4652,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -4663,9 +4663,7 @@
       <c r="G100" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="H100" s="1" t="n">
-        <v>46292</v>
-      </c>
+      <c r="H100" t="inlineStr"/>
       <c r="I100" t="inlineStr"/>
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr"/>
@@ -4680,7 +4678,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Nova Logistics</t>
+          <t>Silver Media</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -4690,7 +4688,7 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4700,13 +4698,15 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G101" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="H101" t="inlineStr"/>
+      <c r="H101" s="1" t="n">
+        <v>46287</v>
+      </c>
       <c r="I101" t="inlineStr"/>
       <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr"/>
@@ -4721,22 +4721,22 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Blue Bank</t>
+          <t>Lumen Logistics</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -4762,17 +4762,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cedar Media</t>
+          <t>Silver Analytics</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G103" s="1" t="n">
@@ -4803,17 +4803,17 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Vertex Retail</t>
+          <t>Cedar Retail</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4823,16 +4823,20 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G104" s="1" t="n">
         <v>46279</v>
       </c>
-      <c r="H104" t="inlineStr"/>
+      <c r="H104" s="1" t="n">
+        <v>46288</v>
+      </c>
       <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
+      <c r="K104" s="1" t="n">
+        <v>46290</v>
+      </c>
       <c r="L104" t="inlineStr"/>
       <c r="M104" t="inlineStr"/>
     </row>
@@ -4844,7 +4848,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Summit Analytics</t>
+          <t>Cedar Health</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -4854,28 +4858,26 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G105" s="1" t="n">
-        <v>46279</v>
+        <v>46280</v>
       </c>
       <c r="H105" t="inlineStr"/>
       <c r="I105" t="inlineStr"/>
       <c r="J105" t="inlineStr"/>
-      <c r="K105" s="1" t="n">
-        <v>46292</v>
-      </c>
+      <c r="K105" t="inlineStr"/>
       <c r="L105" t="inlineStr"/>
       <c r="M105" t="inlineStr"/>
     </row>
@@ -4887,12 +4889,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Summit Logistics</t>
+          <t>Lumen Bank</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -4907,11 +4909,11 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G106" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="H106" t="inlineStr"/>
       <c r="I106" t="inlineStr"/>
@@ -4928,7 +4930,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Nova Insurance</t>
+          <t>Quantum Retail</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -4938,7 +4940,7 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4948,11 +4950,11 @@
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G107" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="H107" t="inlineStr"/>
       <c r="I107" t="inlineStr"/>
@@ -4969,17 +4971,17 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Nova Media</t>
+          <t>Cedar Bank</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4993,7 +4995,7 @@
         </is>
       </c>
       <c r="G108" s="1" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="H108" t="inlineStr"/>
       <c r="I108" t="inlineStr"/>
@@ -5010,31 +5012,31 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cedar Mobility</t>
+          <t>Cedar Media</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G109" s="1" t="n">
-        <v>46282</v>
+        <v>46281</v>
       </c>
       <c r="H109" t="inlineStr"/>
       <c r="I109" t="inlineStr"/>
@@ -5051,22 +5053,22 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Harbor Bank</t>
+          <t>Atlas Analytics</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Analytics Engineer</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -5092,27 +5094,27 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Quantum Health</t>
+          <t>Blue Mobility</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Reporting Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G111" s="1" t="n">
@@ -5133,12 +5135,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cedar Retail</t>
+          <t>Harbor Health</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -5157,7 +5159,7 @@
         </is>
       </c>
       <c r="G112" s="1" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="H112" t="inlineStr"/>
       <c r="I112" t="inlineStr"/>
@@ -5174,31 +5176,31 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Blue Energy</t>
+          <t>Blue Insurance</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Welcome to the Jungle</t>
         </is>
       </c>
       <c r="G113" s="1" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="H113" t="inlineStr"/>
       <c r="I113" t="inlineStr"/>
@@ -5215,7 +5217,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Silver Mobility</t>
+          <t>Lumen Energy</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -5235,18 +5237,16 @@
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G114" s="1" t="n">
-        <v>46283</v>
+        <v>46282</v>
       </c>
       <c r="H114" t="inlineStr"/>
       <c r="I114" t="inlineStr"/>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" s="1" t="n">
-        <v>46295</v>
-      </c>
+      <c r="K114" t="inlineStr"/>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr"/>
     </row>
@@ -5258,31 +5258,31 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Vertex Insurance</t>
+          <t>Lumen Mobility</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G115" s="1" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr"/>
@@ -5299,7 +5299,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Summit Energy</t>
+          <t>Harbor Retail</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -5319,11 +5319,11 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G116" s="1" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr"/>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>North Logistics</t>
+          <t>Nova Bank</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -5360,15 +5360,13 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="G117" s="1" t="n">
         <v>46286</v>
       </c>
-      <c r="H117" s="1" t="n">
-        <v>46288</v>
-      </c>
+      <c r="H117" t="inlineStr"/>
       <c r="I117" t="inlineStr"/>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
@@ -5383,17 +5381,17 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Nova Mobility</t>
+          <t>Vertex Energy</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -5403,7 +5401,7 @@
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G118" s="1" t="n">
@@ -5424,22 +5422,22 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Silver Health</t>
+          <t>Blue Energy</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -5465,22 +5463,22 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Atlas Retail</t>
+          <t>Vertex Logistics</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -5506,12 +5504,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Blue Logistics</t>
+          <t>Vertex Logistics</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -5521,20 +5519,18 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G121" s="1" t="n">
         <v>46286</v>
       </c>
-      <c r="H121" s="1" t="n">
-        <v>46290</v>
-      </c>
+      <c r="H121" t="inlineStr"/>
       <c r="I121" t="inlineStr"/>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
@@ -5549,12 +5545,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>North Analytics</t>
+          <t>Summit Analytics</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -5569,7 +5565,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Referral</t>
         </is>
       </c>
       <c r="G122" s="1" t="n">
@@ -5590,7 +5586,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Atlas Bank</t>
+          <t>Blue Energy</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -5600,7 +5596,7 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -5610,11 +5606,11 @@
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G123" s="1" t="n">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="H123" t="inlineStr"/>
       <c r="I123" t="inlineStr"/>
@@ -5631,17 +5627,17 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Cedar Analytics</t>
+          <t>Summit Media</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5651,11 +5647,11 @@
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G124" s="1" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="H124" t="inlineStr"/>
       <c r="I124" t="inlineStr"/>
@@ -5672,12 +5668,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Bright Health</t>
+          <t>Vertex Media</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -5696,7 +5692,7 @@
         </is>
       </c>
       <c r="G125" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="H125" t="inlineStr"/>
       <c r="I125" t="inlineStr"/>
@@ -5713,31 +5709,31 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Lumen Labs</t>
+          <t>Bright Health</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Recruiter</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G126" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="H126" t="inlineStr"/>
       <c r="I126" t="inlineStr"/>
@@ -5754,17 +5750,17 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Vertex Logistics</t>
+          <t>North Mobility</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5774,11 +5770,11 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G127" s="1" t="n">
-        <v>46287</v>
+        <v>46288</v>
       </c>
       <c r="H127" t="inlineStr"/>
       <c r="I127" t="inlineStr"/>
@@ -5795,12 +5791,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Nova Health</t>
+          <t>Blue Mobility</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -5810,16 +5806,16 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G128" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H128" t="inlineStr"/>
       <c r="I128" t="inlineStr"/>
@@ -5836,17 +5832,17 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Vertex Mobility</t>
+          <t>Summit Logistics</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5860,7 +5856,7 @@
         </is>
       </c>
       <c r="G129" s="1" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="H129" t="inlineStr"/>
       <c r="I129" t="inlineStr"/>
@@ -5877,12 +5873,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Lumen Insurance</t>
+          <t>Bright Retail</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -5892,16 +5888,16 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>On-site</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G130" s="1" t="n">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="H130" t="inlineStr"/>
       <c r="I130" t="inlineStr"/>
@@ -5918,31 +5914,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Cedar Energy</t>
+          <t>Bright Media</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Analytics Engineer</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Lille</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G131" s="1" t="n">
-        <v>46293</v>
+        <v>46290</v>
       </c>
       <c r="H131" t="inlineStr"/>
       <c r="I131" t="inlineStr"/>
@@ -5959,7 +5955,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Lumen Bank</t>
+          <t>Cedar Mobility</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5969,7 +5965,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Lille</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5979,7 +5975,7 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G132" s="1" t="n">
@@ -6000,7 +5996,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Atlas Media</t>
+          <t>Quantum Labs</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -6010,17 +6006,17 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Lyon</t>
+          <t>Amsterdam</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G133" s="1" t="n">
@@ -6041,12 +6037,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Atlas Bank</t>
+          <t>Summit Mobility</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -6061,7 +6057,7 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="G134" s="1" t="n">
@@ -6082,17 +6078,17 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Cedar Logistics</t>
+          <t>Blue Health</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>Reporting Analyst</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -6102,7 +6098,7 @@
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Company website</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="G135" s="1" t="n">
@@ -6123,35 +6119,33 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Vertex Mobility</t>
+          <t>Summit Energy</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Data Analyst</t>
+          <t>BI Analyst</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Welcome to the Jungle</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G136" s="1" t="n">
         <v>46294</v>
       </c>
-      <c r="H136" s="1" t="n">
-        <v>46296</v>
-      </c>
+      <c r="H136" t="inlineStr"/>
       <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr"/>
@@ -6166,27 +6160,27 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Bright Energy</t>
+          <t>Silver Analytics</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Company website</t>
         </is>
       </c>
       <c r="G137" s="1" t="n">
@@ -6207,12 +6201,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Lumen Insurance</t>
+          <t>Bright Logistics</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -6227,7 +6221,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>LinkedIn Easy Apply</t>
         </is>
       </c>
       <c r="G138" s="1" t="n">
@@ -6248,22 +6242,22 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Silver Energy</t>
+          <t>Lumen Mobility</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Junior Data Engineer</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>London</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>Remote</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -6289,27 +6283,27 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Harbor Labs</t>
+          <t>Blue Retail</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Junior Data Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Paris</t>
+          <t>Lyon</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Hybrid</t>
+          <t>On-site</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="G140" s="1" t="n">
@@ -6330,17 +6324,17 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>North Bank</t>
+          <t>Nova Retail</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>BI Analyst</t>
+          <t>Data Analyst</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Amsterdam</t>
+          <t>London</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -6350,7 +6344,7 @@
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Indeed</t>
+          <t>Recruiter</t>
         </is>
       </c>
       <c r="G141" s="1" t="n">
@@ -6371,36 +6365,38 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Silver Analytics</t>
+          <t>Summit Energy</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Junior Data Engineer</t>
+          <t>Junior Data Analyst</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Remote</t>
+          <t>Hybrid</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>LinkedIn Easy Apply</t>
+          <t>Indeed</t>
         </is>
       </c>
       <c r="G142" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="H142" t="inlineStr"/>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
-      <c r="K142" t="inlineStr"/>
+      <c r="K142" s="1" t="n">
+        <v>46293</v>
+      </c>
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr"/>
     </row>
